--- a/patient_registration_form_templates/039_hospital_admission_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/039_hospital_admission_form--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1286,8 +1286,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'general_practitioner',_'label':_'general_practitioner'}</t>
+          <t>general_practitioner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'general_practitioner', 'label': 'General Practitioner'}</t>
+          <t>General Practitioner</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'specialist',_'label':_'specialist'}</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'specialist', 'label': 'Specialist'}</t>
+          <t>Specialist</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'nurse',_'label':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'nurse', 'label': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'unknown',_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'unknown', 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_'cardiology',_'label':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': 'cardiology', 'label': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_28,_'name':_'general_medicine',_'label':_'general_medicine'}</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 28, 'name': 'general_medicine', 'label': 'General Medicine'}</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_29,_'name':_'neurology',_'label':_'neurology'}</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 29, 'name': 'neurology', 'label': 'Neurology'}</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_39,_'name':_'father',_'label':_'father'}</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 39, 'name': 'father', 'label': 'Father'}</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'mother',_'label':_'mother'}</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'mother', 'label': 'Mother'}</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_'brother',_'label':_'brother'}</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 'brother', 'label': 'Brother'}</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_'sister',_'label':_'sister'}</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 'sister', 'label': 'Sister'}</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_43,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 43, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_44,_'name':_'spouse',_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 44, 'name': 'spouse', 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_45,_'name':_'unknown',_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 45, 'name': 'unknown', 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
